--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/WISCONSIN_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/WISCONSIN_2019.xlsx
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C240">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C665">
@@ -18913,7 +18913,7 @@
         <v>95</v>
       </c>
       <c r="D1031">
-        <v>0.009936199142349127</v>
+        <v>0.009936199142349129</v>
       </c>
     </row>
     <row r="1032">
